--- a/codegen/__out__/pc/public/import_template/base/usr.xlsx
+++ b/codegen/__out__/pc/public/import_template/base/usr.xlsx
@@ -43,6 +43,9 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;%=comment.dept_ids_lbl%&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;%=comment.tenant_id_lbl%&gt;&lt;%selectList.tenant_id = data.findAllTenant.map((item) =&gt; item.lbl)%&gt;&lt;%_dataValidation_({ sqref: `${ _col }2:${ _col }${ _lastRow }`, formula1: `"${ selectList.tenant_id.join(",") }"` })%&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;%=comment.role_ids_lbl%&gt;</t>
@@ -398,6 +401,9 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/codegen/__out__/pc/public/import_template/base/usr.xlsx
+++ b/codegen/__out__/pc/public/import_template/base/usr.xlsx
@@ -43,9 +43,6 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;%=comment.dept_ids_lbl%&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;%=comment.tenant_id_lbl%&gt;&lt;%selectList.tenant_id = data.findAllTenant.map((item) =&gt; item.lbl)%&gt;&lt;%_dataValidation_({ sqref: `${ _col }2:${ _col }${ _lastRow }`, formula1: `"${ selectList.tenant_id.join(",") }"` })%&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;%=comment.role_ids_lbl%&gt;</t>
@@ -401,9 +398,6 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
